--- a/sheets/조재수대금교본/검수/천년바위 (3).xlsx
+++ b/sheets/조재수대금교본/검수/천년바위 (3).xlsx
@@ -6806,7 +6806,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -6821,21 +6821,13 @@
         </is>
       </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
@@ -6844,16 +6836,11 @@
     </row>
     <row r="5" ht="100.96" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -6861,11 +6848,7 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21"/>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
@@ -6894,11 +6877,7 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -6906,11 +6885,7 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -6918,11 +6893,7 @@
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="100.96" customHeight="true">
@@ -6938,7 +6909,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰∽</t>
+汰</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -6979,23 +6950,14 @@
     </row>
     <row r="8" ht="100.96" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -7006,16 +6968,11 @@
         </is>
       </c>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -7038,19 +6995,19 @@
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-汰∽</t>
+汰</t>
         </is>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -7064,7 +7021,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-汰∽</t>
+汰</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -7101,8 +7058,7 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="23"/>
@@ -7141,8 +7097,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-ﾉ
+          <t xml:space="preserve">㳞
 –</t>
         </is>
       </c>
@@ -7150,8 +7105,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -7161,7 +7115,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋⌝
+          <t xml:space="preserve">淋
 汰㳞</t>
         </is>
       </c>
@@ -7171,7 +7125,7 @@
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -7206,7 +7160,7 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -7238,47 +7192,19 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
     <row r="15" ht="6.0" customHeight="true">
@@ -7324,7 +7250,7 @@
       <c r="E17" s="22"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G17" s="22"/>
@@ -7343,7 +7269,7 @@
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M17" s="22"/>
@@ -7356,7 +7282,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -7371,21 +7297,13 @@
         </is>
       </c>
       <c r="E18" s="23"/>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F18" s="21"/>
       <c r="G18" s="23"/>
       <c r="H18" s="21"/>
       <c r="I18" s="23"/>
       <c r="J18" s="21"/>
       <c r="K18" s="23"/>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L18" s="21"/>
       <c r="M18" s="23"/>
       <c r="N18" s="21"/>
       <c r="O18" s="23"/>
@@ -7394,32 +7312,19 @@
     </row>
     <row r="19" ht="100.96" customHeight="true">
       <c r="A19" s="0"/>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="B19" s="21"/>
       <c r="C19" s="24"/>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="21"/>
       <c r="G19" s="24"/>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="H19" s="21"/>
       <c r="I19" s="24"/>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="J19" s="21"/>
       <c r="K19" s="24"/>
       <c r="L19" s="21"/>
       <c r="M19" s="24"/>
@@ -7438,7 +7343,7 @@
       <c r="C20" s="22"/>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E20" s="22"/>
@@ -7460,11 +7365,7 @@
         </is>
       </c>
       <c r="K20" s="22"/>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L20" s="21"/>
       <c r="M20" s="22"/>
       <c r="N20" s="21" t="inlineStr">
         <is>
@@ -7472,11 +7373,7 @@
         </is>
       </c>
       <c r="O20" s="22"/>
-      <c r="P20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
     </row>
     <row r="21" ht="100.96" customHeight="true">
@@ -7492,7 +7389,7 @@
       <c r="F21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰∽</t>
+汰</t>
         </is>
       </c>
       <c r="G21" s="23"/>
@@ -7528,23 +7425,14 @@
     </row>
     <row r="22" ht="100.96" customHeight="true">
       <c r="A22" s="0"/>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B22" s="21"/>
       <c r="C22" s="24"/>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D22" s="21"/>
       <c r="E22" s="24"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="G22" s="24"/>
@@ -7555,16 +7443,11 @@
         </is>
       </c>
       <c r="I22" s="24"/>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J22" s="21"/>
       <c r="K22" s="24"/>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M22" s="24"/>
@@ -7593,13 +7476,13 @@
       <c r="C23" s="22"/>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="G23" s="22"/>
@@ -7613,13 +7496,13 @@
       <c r="J23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㳞
-汰∽</t>
+汰</t>
         </is>
       </c>
       <c r="K23" s="22"/>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M23" s="22"/>
@@ -7650,8 +7533,7 @@
       <c r="E24" s="23"/>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G24" s="23"/>
@@ -7690,8 +7572,7 @@
       <c r="C25" s="24"/>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-ﾉ
+          <t xml:space="preserve">㳞
 –</t>
         </is>
       </c>
@@ -7699,8 +7580,7 @@
       <c r="F25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="G25" s="24"/>
@@ -7710,7 +7590,7 @@
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋⌝
+          <t xml:space="preserve">淋
 汰㳞</t>
         </is>
       </c>
@@ -7720,7 +7600,7 @@
       <c r="P25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="Q25" s="24"/>
@@ -7731,7 +7611,7 @@
       <c r="C26" s="22"/>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E26" s="22"/>
@@ -7755,7 +7635,7 @@
       <c r="O26" s="22"/>
       <c r="P26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q26" s="22"/>
@@ -7787,47 +7667,19 @@
         </is>
       </c>
       <c r="C28" s="24"/>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D28" s="21"/>
       <c r="E28" s="24"/>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F28" s="21"/>
       <c r="G28" s="24"/>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H28" s="21"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N28" s="21"/>
       <c r="O28" s="24"/>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
     </row>
     <row r="29" ht="6.0" customHeight="true">
@@ -7879,7 +7731,7 @@
       <c r="K31" s="22"/>
       <c r="L31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M31" s="22"/>
@@ -7892,7 +7744,7 @@
       <c r="O31" s="22"/>
       <c r="P31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q31" s="22"/>
@@ -7909,11 +7761,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="21"/>
       <c r="K32" s="23"/>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L32" s="21"/>
       <c r="M32" s="23"/>
       <c r="N32" s="21"/>
       <c r="O32" s="23"/>
@@ -7928,17 +7776,9 @@
       <c r="E33" s="24"/>
       <c r="F33" s="21"/>
       <c r="G33" s="24"/>
-      <c r="H33" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="H33" s="21"/>
       <c r="I33" s="24"/>
-      <c r="J33" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="J33" s="21"/>
       <c r="K33" s="24"/>
       <c r="L33" s="21"/>
       <c r="M33" s="24"/>
@@ -7957,7 +7797,7 @@
       <c r="G34" s="22"/>
       <c r="H34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㅂ∼</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="I34" s="22"/>
@@ -7967,23 +7807,15 @@
         </is>
       </c>
       <c r="K34" s="22"/>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L34" s="21"/>
       <c r="M34" s="22"/>
       <c r="N34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞⊏∼</t>
+          <t xml:space="preserve">㳞∼</t>
         </is>
       </c>
       <c r="O34" s="22"/>
-      <c r="P34" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P34" s="21"/>
       <c r="Q34" s="22"/>
     </row>
     <row r="35" ht="100.96" customHeight="true">
@@ -7999,7 +7831,7 @@
       <c r="J35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰∽</t>
+汰</t>
         </is>
       </c>
       <c r="K35" s="23"/>
@@ -8013,7 +7845,7 @@
       <c r="N35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-c㳞㳞c</t>
+㳞㳞</t>
         </is>
       </c>
       <c r="O35" s="23"/>
@@ -8033,11 +7865,7 @@
       <c r="E36" s="24"/>
       <c r="F36" s="21"/>
       <c r="G36" s="24"/>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H36" s="21"/>
       <c r="I36" s="24"/>
       <c r="J36" s="21" t="inlineStr">
         <is>
@@ -8047,14 +7875,13 @@
       <c r="K36" s="24"/>
       <c r="L36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M36" s="24"/>
       <c r="N36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞⊏∼</t>
+          <t xml:space="preserve">㳞∼</t>
         </is>
       </c>
       <c r="O36" s="24"/>
@@ -8095,7 +7922,7 @@
       <c r="M37" s="22"/>
       <c r="N37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽太南
+          <t xml:space="preserve">太南
 –</t>
         </is>
       </c>
@@ -8154,7 +7981,7 @@
       <c r="K39" s="24"/>
       <c r="L39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋⌝
+          <t xml:space="preserve">淋
 汰㳞</t>
         </is>
       </c>
@@ -8164,7 +7991,7 @@
       <c r="P39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="Q39" s="24"/>
@@ -8191,7 +8018,7 @@
       <c r="O40" s="22"/>
       <c r="P40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q40" s="22"/>
@@ -8235,23 +8062,11 @@
         </is>
       </c>
       <c r="K42" s="24"/>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L42" s="21"/>
       <c r="M42" s="24"/>
-      <c r="N42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N42" s="21"/>
       <c r="O42" s="24"/>
-      <c r="P42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P42" s="21"/>
       <c r="Q42" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/천년바위 (3).xlsx
+++ b/sheets/조재수대금교본/검수/천년바위 (3).xlsx
@@ -6806,7 +6806,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ∽</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -6821,13 +6821,21 @@
         </is>
       </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
@@ -6836,11 +6844,16 @@
     </row>
     <row r="5" ht="100.96" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -6848,7 +6861,11 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21"/>
       <c r="I5" s="24"/>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
@@ -6877,7 +6894,11 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -6885,7 +6906,11 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -6893,7 +6918,11 @@
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="100.96" customHeight="true">
@@ -6909,7 +6938,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+汰∽</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -6995,19 +7024,19 @@
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-汰</t>
+汰∽</t>
         </is>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -7021,7 +7050,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-汰</t>
+汰∽</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -7058,7 +7087,8 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="G10" s="23"/>
@@ -7097,7 +7127,8 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ʒ
+ﾉ
 –</t>
         </is>
       </c>
@@ -7115,7 +7146,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋⌝
 汰㳞</t>
         </is>
       </c>
@@ -7125,7 +7156,7 @@
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -7160,7 +7191,7 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -7250,7 +7281,7 @@
       <c r="E17" s="22"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="G17" s="22"/>
@@ -7269,7 +7300,7 @@
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="M17" s="22"/>
@@ -7282,7 +7313,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ∽</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -7297,13 +7328,21 @@
         </is>
       </c>
       <c r="E18" s="23"/>
-      <c r="F18" s="21"/>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G18" s="23"/>
       <c r="H18" s="21"/>
       <c r="I18" s="23"/>
       <c r="J18" s="21"/>
       <c r="K18" s="23"/>
-      <c r="L18" s="21"/>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M18" s="23"/>
       <c r="N18" s="21"/>
       <c r="O18" s="23"/>
@@ -7312,19 +7351,32 @@
     </row>
     <row r="19" ht="100.96" customHeight="true">
       <c r="A19" s="0"/>
-      <c r="B19" s="21"/>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C19" s="24"/>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="21"/>
       <c r="G19" s="24"/>
-      <c r="H19" s="21"/>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I19" s="24"/>
-      <c r="J19" s="21"/>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K19" s="24"/>
       <c r="L19" s="21"/>
       <c r="M19" s="24"/>
@@ -7343,7 +7395,7 @@
       <c r="C20" s="22"/>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="E20" s="22"/>
@@ -7365,7 +7417,11 @@
         </is>
       </c>
       <c r="K20" s="22"/>
-      <c r="L20" s="21"/>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M20" s="22"/>
       <c r="N20" s="21" t="inlineStr">
         <is>
@@ -7373,7 +7429,11 @@
         </is>
       </c>
       <c r="O20" s="22"/>
-      <c r="P20" s="21"/>
+      <c r="P20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q20" s="22"/>
     </row>
     <row r="21" ht="100.96" customHeight="true">
@@ -7389,7 +7449,7 @@
       <c r="F21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+汰∽</t>
         </is>
       </c>
       <c r="G21" s="23"/>
@@ -7476,13 +7536,13 @@
       <c r="C23" s="22"/>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="G23" s="22"/>
@@ -7496,13 +7556,13 @@
       <c r="J23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㳞
-汰</t>
+汰∽</t>
         </is>
       </c>
       <c r="K23" s="22"/>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="M23" s="22"/>
@@ -7533,7 +7593,8 @@
       <c r="E24" s="23"/>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="G24" s="23"/>
@@ -7572,7 +7633,8 @@
       <c r="C25" s="24"/>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ʒ
+ﾉ
 –</t>
         </is>
       </c>
@@ -7590,7 +7652,7 @@
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋⌝
 汰㳞</t>
         </is>
       </c>
@@ -7600,7 +7662,7 @@
       <c r="P25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="Q25" s="24"/>
@@ -7611,7 +7673,7 @@
       <c r="C26" s="22"/>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="E26" s="22"/>
@@ -7635,7 +7697,7 @@
       <c r="O26" s="22"/>
       <c r="P26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="Q26" s="22"/>
@@ -7731,7 +7793,7 @@
       <c r="K31" s="22"/>
       <c r="L31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="M31" s="22"/>
@@ -7744,7 +7806,7 @@
       <c r="O31" s="22"/>
       <c r="P31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ∽</t>
         </is>
       </c>
       <c r="Q31" s="22"/>
@@ -7761,7 +7823,11 @@
       <c r="I32" s="23"/>
       <c r="J32" s="21"/>
       <c r="K32" s="23"/>
-      <c r="L32" s="21"/>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M32" s="23"/>
       <c r="N32" s="21"/>
       <c r="O32" s="23"/>
@@ -7776,9 +7842,17 @@
       <c r="E33" s="24"/>
       <c r="F33" s="21"/>
       <c r="G33" s="24"/>
-      <c r="H33" s="21"/>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I33" s="24"/>
-      <c r="J33" s="21"/>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K33" s="24"/>
       <c r="L33" s="21"/>
       <c r="M33" s="24"/>
@@ -7797,7 +7871,7 @@
       <c r="G34" s="22"/>
       <c r="H34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼</t>
+          <t xml:space="preserve">南ㅂ∼</t>
         </is>
       </c>
       <c r="I34" s="22"/>
@@ -7807,15 +7881,23 @@
         </is>
       </c>
       <c r="K34" s="22"/>
-      <c r="L34" s="21"/>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M34" s="22"/>
       <c r="N34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞∼</t>
+          <t xml:space="preserve">㳞⊏∼</t>
         </is>
       </c>
       <c r="O34" s="22"/>
-      <c r="P34" s="21"/>
+      <c r="P34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q34" s="22"/>
     </row>
     <row r="35" ht="100.96" customHeight="true">
@@ -7831,7 +7913,7 @@
       <c r="J35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+汰∽</t>
         </is>
       </c>
       <c r="K35" s="23"/>
@@ -7845,7 +7927,7 @@
       <c r="N35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞㳞</t>
+c㳞㳞c</t>
         </is>
       </c>
       <c r="O35" s="23"/>
@@ -7881,7 +7963,7 @@
       <c r="M36" s="24"/>
       <c r="N36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞∼</t>
+          <t xml:space="preserve">㳞⊏∼</t>
         </is>
       </c>
       <c r="O36" s="24"/>
@@ -7922,7 +8004,7 @@
       <c r="M37" s="22"/>
       <c r="N37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太南
+          <t xml:space="preserve">∽太南
 –</t>
         </is>
       </c>
@@ -7981,7 +8063,7 @@
       <c r="K39" s="24"/>
       <c r="L39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋⌝
 汰㳞</t>
         </is>
       </c>
@@ -7991,7 +8073,7 @@
       <c r="P39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="Q39" s="24"/>
@@ -8018,7 +8100,7 @@
       <c r="O40" s="22"/>
       <c r="P40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="Q40" s="22"/>

--- a/sheets/조재수대금교본/검수/천년바위 (3).xlsx
+++ b/sheets/조재수대금교본/검수/천년바위 (3).xlsx
@@ -6714,28 +6714,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="16.2" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.2" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="16.2" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="67.8" customHeight="true">
+    <row r="2" ht="85.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="100.96" customHeight="true">
+    <row r="3" ht="126.87" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="100.96" customHeight="true">
+    <row r="4" ht="126.87" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -6842,7 +6842,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="100.96" customHeight="true">
+    <row r="5" ht="126.87" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="100.96" customHeight="true">
+    <row r="6" ht="126.87" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="100.96" customHeight="true">
+    <row r="7" ht="126.87" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="100.96" customHeight="true">
+    <row r="8" ht="126.87" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="100.96" customHeight="true">
+    <row r="9" ht="126.87" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="100.96" customHeight="true">
+    <row r="10" ht="126.87" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="100.96" customHeight="true">
+    <row r="11" ht="126.87" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="100.96" customHeight="true">
+    <row r="12" ht="126.87" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="100.96" customHeight="true">
+    <row r="13" ht="126.87" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -7215,7 +7215,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="100.96" customHeight="true">
+    <row r="14" ht="126.87" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="67.8" customHeight="true">
+    <row r="16" ht="85.11" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="100.96" customHeight="true">
+    <row r="17" ht="126.87" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="100.96" customHeight="true">
+    <row r="18" ht="126.87" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -7349,7 +7349,7 @@
       <c r="P18" s="21"/>
       <c r="Q18" s="23"/>
     </row>
-    <row r="19" ht="100.96" customHeight="true">
+    <row r="19" ht="126.87" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="100.96" customHeight="true">
+    <row r="20" ht="126.87" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="100.96" customHeight="true">
+    <row r="21" ht="126.87" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="100.96" customHeight="true">
+    <row r="22" ht="126.87" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="100.96" customHeight="true">
+    <row r="23" ht="126.87" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="Q23" s="22"/>
     </row>
-    <row r="24" ht="100.96" customHeight="true">
+    <row r="24" ht="126.87" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="Q24" s="23"/>
     </row>
-    <row r="25" ht="100.96" customHeight="true">
+    <row r="25" ht="126.87" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="100.96" customHeight="true">
+    <row r="26" ht="126.87" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="100.96" customHeight="true">
+    <row r="27" ht="126.87" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -7721,7 +7721,7 @@
       <c r="P27" s="21"/>
       <c r="Q27" s="23"/>
     </row>
-    <row r="28" ht="100.96" customHeight="true">
+    <row r="28" ht="126.87" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
     <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="67.8" customHeight="true">
+    <row r="30" ht="85.11" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
       <c r="P30" s="20"/>
       <c r="Q30" s="20"/>
     </row>
-    <row r="31" ht="100.96" customHeight="true">
+    <row r="31" ht="126.87" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Q31" s="22"/>
     </row>
-    <row r="32" ht="100.96" customHeight="true">
+    <row r="32" ht="126.87" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="23"/>
@@ -7834,7 +7834,7 @@
       <c r="P32" s="21"/>
       <c r="Q32" s="23"/>
     </row>
-    <row r="33" ht="100.96" customHeight="true">
+    <row r="33" ht="126.87" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="24"/>
@@ -7861,7 +7861,7 @@
       <c r="P33" s="21"/>
       <c r="Q33" s="24"/>
     </row>
-    <row r="34" ht="100.96" customHeight="true">
+    <row r="34" ht="126.87" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="Q34" s="22"/>
     </row>
-    <row r="35" ht="100.96" customHeight="true">
+    <row r="35" ht="126.87" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="Q35" s="23"/>
     </row>
-    <row r="36" ht="100.96" customHeight="true">
+    <row r="36" ht="126.87" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="Q36" s="24"/>
     </row>
-    <row r="37" ht="100.96" customHeight="true">
+    <row r="37" ht="126.87" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21"/>
       <c r="C37" s="22"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="Q37" s="22"/>
     </row>
-    <row r="38" ht="100.96" customHeight="true">
+    <row r="38" ht="126.87" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="23"/>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="Q38" s="23"/>
     </row>
-    <row r="39" ht="100.96" customHeight="true">
+    <row r="39" ht="126.87" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="24"/>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="Q39" s="24"/>
     </row>
-    <row r="40" ht="100.96" customHeight="true">
+    <row r="40" ht="126.87" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="22"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="Q40" s="22"/>
     </row>
-    <row r="41" ht="100.96" customHeight="true">
+    <row r="41" ht="126.87" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="23"/>
@@ -8124,7 +8124,7 @@
       <c r="P41" s="21"/>
       <c r="Q41" s="23"/>
     </row>
-    <row r="42" ht="100.96" customHeight="true">
+    <row r="42" ht="126.87" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="24"/>
@@ -8159,7 +8159,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="59"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="47"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
